--- a/datos/COMISION.xlsx
+++ b/datos/COMISION.xlsx
@@ -11,12 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t xml:space="preserve">CODIGO </t>
   </si>
   <si>
     <t>COMISION</t>
+  </si>
+  <si>
+    <t>ADBLUE</t>
   </si>
 </sst>
 </file>
@@ -59,12 +62,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
@@ -77,6 +80,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -140,7 +146,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C2:D35" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C2:D36" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="2">
     <tableColumn name="CODIGO " id="1"/>
     <tableColumn name="COMISION" id="2"/>
@@ -352,7 +358,7 @@
   <cols>
     <col customWidth="1" min="1" max="2" width="10.71"/>
     <col customWidth="1" min="3" max="3" width="18.71"/>
-    <col customWidth="1" min="4" max="26" width="10.71"/>
+    <col customWidth="1" min="4" max="6" width="10.71"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -627,7 +633,14 @@
         <v>600.0</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="C36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="4">
+        <v>16.0</v>
+      </c>
+    </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1"/>

--- a/datos/COMISION.xlsx
+++ b/datos/COMISION.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">CODIGO </t>
   </si>
@@ -20,6 +20,9 @@
   </si>
   <si>
     <t>ADBLUE</t>
+  </si>
+  <si>
+    <t>Krynex Agua Verde 6x</t>
   </si>
 </sst>
 </file>
@@ -146,7 +149,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C2:D36" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C2:D37" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="2">
     <tableColumn name="CODIGO " id="1"/>
     <tableColumn name="COMISION" id="2"/>
@@ -641,7 +644,14 @@
         <v>16.0</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="C37" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="4">
+        <v>200.0</v>
+      </c>
+    </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>

--- a/datos/COMISION.xlsx
+++ b/datos/COMISION.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
   <si>
     <t xml:space="preserve">CODIGO </t>
   </si>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C2:D37" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C2:D47" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="2">
     <tableColumn name="CODIGO " id="1"/>
     <tableColumn name="COMISION" id="2"/>
@@ -637,31 +637,101 @@
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="4">
-        <v>16.0</v>
+      <c r="D36" s="5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="4">
         <v>200.0</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="C38" s="6">
+        <v>967072.0</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1000.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="C39" s="6">
+        <v>965358.0</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1000.0</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="C40" s="6">
+        <v>9367.0</v>
+      </c>
+      <c r="D40" s="4">
+        <v>500.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="C41" s="6">
+        <v>9366.0</v>
+      </c>
+      <c r="D41" s="4">
+        <v>500.0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="C42" s="6">
+        <v>9370.0</v>
+      </c>
+      <c r="D42" s="4">
+        <v>500.0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="C43" s="6">
+        <v>9369.0</v>
+      </c>
+      <c r="D43" s="4">
+        <v>500.0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="C44" s="6">
+        <v>9368.0</v>
+      </c>
+      <c r="D44" s="4">
+        <v>500.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="C45" s="6">
+        <v>9373.0</v>
+      </c>
+      <c r="D45" s="4">
+        <v>300.0</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="C46" s="6">
+        <v>9371.0</v>
+      </c>
+      <c r="D46" s="4">
+        <v>300.0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="C47" s="6">
+        <v>9372.0</v>
+      </c>
+      <c r="D47" s="4">
+        <v>300.0</v>
+      </c>
+    </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>

--- a/datos/COMISION.xlsx
+++ b/datos/COMISION.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">CODIGO </t>
   </si>
@@ -640,8 +640,8 @@
       <c r="C36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>2</v>
+      <c r="D36" s="4">
+        <v>16.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
